--- a/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules arrive au parc. Papa lui montre un espace. Papa dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Jules va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Papa voit Jules. L'adulte voit. Jules verse le sable. Il fait un gâteau. Le sable est frais. Jules reste dans l'espace. Papa dit : je te vois. Jules sourit. Il reste là. Les mains sont dans le sable.</t>
+          <t>Jules arrive au parc. Papa lui montre un espace. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Jules va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Papa voit Jules. L'adulte voit. Jules verse le sable. Il fait un gâteau. Le sable est frais. Jules reste dans l'espace. Je te vois. Jules sourit. Il reste là. Les mains sont dans le sable.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules arrive au parc. Papa lui montre un espace.
+papa|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
+narrateur|Jules va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Papa voit Jules. L'adulte voit. Jules verse le sable. Il fait un gâteau. Le sable est frais. Jules reste dans l'espace.
+papa|Je te vois.
+narrateur|Jules sourit. Il reste là. Les mains sont dans le sable.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jules joue au parc. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est dans l'espace montré. Papa le voit. Le gâteau de sable est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range le seau. Papa lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Jules sourit. Il reste là. Les mains sont dans le sable.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Jules joue au parc. Où joue-t-il ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -1668,6 +1683,7 @@
           <t>narrateur|Jules est dans l'espace montré. Papa le voit. Le gâteau de sable est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1851,7 @@
           <t>narrateur|Jules range le seau. Papa lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules joue dans l'espace</t>
+          <t>Le seau jaune de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le seau jaune de Nino va au bac à sable. Papa montre l'espace. Nino reste où l'adulte voit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules arrive au parc. Papa lui montre un espace. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Jules va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Papa voit Jules. L'adulte voit. Jules verse le sable. Il fait un gâteau. Le sable est frais. Jules reste dans l'espace. Je te vois. Jules sourit. Il reste là. Les mains sont dans le sable.</t>
+          <t>Un seau jaune attend près des bottes. Les bottes sont un peu mouillées. Le pain sent bon, loin. L'herbe sent la pluie. Une feuille est collée sur une botte. Tu as vu le seau, Nino ? Il est jaune, papa. Oui. On le prend. Nino prend le seau. Le plastique est lisse. La pelle est dedans. La pelle est rouge. On met tes bottes ? Nino enfile une botte. Puis l'autre botte. Tu as fini tes bottes ? Oui, papa. Bravo. Ils marchent vers le parc. Une goutte tombe d'une feuille. Elle fait tic sur le seau. Tic. Oui. C'est une goutte. En ce moment, ils arrivent au parc. Le bac à sable est là. Le sable est frais. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nino va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Le banc est un peu humide. Papa voit Nino. L'adulte voit. Nino verse le sable. Le sable est frais et un peu froid. Il est froid, papa. Oui. Il est frais. Nino fait un gâteau. Il tape le seau. Ça fait toc toc. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Nino retourne le seau. Le gâteau de sable est là. Il est un peu croulé. Un gâteau ! Beau gâteau. L'adulte voit. Tu as fait du bon travail. Nino reste dans l'espace. Les mains sont dans le sable. Le seau jaune brille un peu. On fait un autre gâteau ? Oui. Nino remplit encore le seau. Il tasse avec la pelle rouge. Il retourne encore le seau. Je te vois encore. Je reste ici. Oui. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules arrive au parc. Papa lui montre un espace.
-papa|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
-narrateur|Jules va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Papa voit Jules. L'adulte voit. Jules verse le sable. Il fait un gâteau. Le sable est frais. Jules reste dans l'espace.
+          <t>narrateur|Un seau jaune attend près des bottes.
+narrateur|Les bottes sont un peu mouillées.
+narrateur|Le pain sent bon, loin.
+narrateur|L'herbe sent la pluie.
+narrateur|Une feuille est collée sur une botte.
+papa|Tu as vu le seau, Nino ?
+enfant-m|Il est jaune, papa.
+papa|Oui.
+papa|On le prend.
+narrateur|Nino prend le seau.
+narrateur|Le plastique est lisse.
+narrateur|La pelle est dedans.
+narrateur|La pelle est rouge.
+papa|On met tes bottes ?
+narrateur|Nino enfile une botte.
+narrateur|Puis l'autre botte.
+papa|Tu as fini tes bottes ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Ils marchent vers le parc.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Elle fait tic sur le seau.
+enfant-m|Tic.
+papa|Oui.
+papa|C'est une goutte.
+narrateur|En ce moment, ils arrivent au parc.
+narrateur|Le bac à sable est là.
+narrateur|Le sable est frais.
+papa|Tu joues ici.
+papa|C'est l'espace montré.
+papa|Ici, l'adulte voit.
+narrateur|Nino va au bac à sable.
+narrateur|Il reste dans l'espace montré.
+narrateur|Papa s'assoit sur le banc.
+narrateur|Le banc est un peu humide.
+narrateur|Papa voit Nino.
+narrateur|L'adulte voit.
+narrateur|Nino verse le sable.
+narrateur|Le sable est frais et un peu froid.
+enfant-m|Il est froid, papa.
+papa|Oui.
+papa|Il est frais.
+narrateur|Nino fait un gâteau.
+narrateur|Il tape le seau.
+narrateur|Ça fait toc toc.
 papa|Je te vois.
-narrateur|Jules sourit. Il reste là. Les mains sont dans le sable.</t>
+papa|Tu restes dans l'espace montré ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Nino retourne le seau.
+narrateur|Le gâteau de sable est là.
+narrateur|Il est un peu croulé.
+enfant-m|Un gâteau !
+papa|Beau gâteau.
+papa|L'adulte voit.
+papa|Tu as fait du bon travail.
+narrateur|Nino reste dans l'espace.
+narrateur|Les mains sont dans le sable.
+narrateur|Le seau jaune brille un peu.
+papa|On fait un autre gâteau ?
+enfant-m|Oui.
+narrateur|Nino remplit encore le seau.
+narrateur|Il tasse avec la pelle rouge.
+narrateur|Il retourne encore le seau.
+papa|Je te vois encore.
+enfant-m|Je reste ici.
+papa|Oui.
+papa|Dans l'espace montré.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jules joue au parc. Où joue-t-il ?</t>
+          <t>Nino joue au parc. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jules joue au parc. Où joue-t-il ?</t>
+          <t>narrateur|Nino joue au parc.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1536,7 +1612,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans l'espace montré. Papa le voit. Le gâteau de sable est là.</t>
+          <t>Nino est dans l'espace montré. Papa le voit. L'adulte voit. Le gâteau de sable est là. Tu as joué dans l'espace montré ? Oui. Bravo. Je te voyais. Le seau jaune a du sable. La pelle est à côté.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1756,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules est dans l'espace montré. Papa le voit. Le gâteau de sable est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino est dans l'espace montré.
+narrateur|Papa le voit.
+narrateur|L'adulte voit.
+narrateur|Le gâteau de sable est là.
+papa|Tu as joué dans l'espace montré ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Je te voyais.
+narrateur|Le seau jaune a du sable.
+narrateur|La pelle est à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules range le seau. Papa lui tend la main.</t>
+          <t>Nino range le seau. Il range la pelle. Papa lui tend la main. Tu as fini le gâteau ? Oui, papa. Bravo. On rentre. Nino prend la main de papa. Le seau jaune tape doucement. L'herbe sent encore la pluie. Tu es resté où je vois. Dans l'espace montré. Oui. L'adulte voit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,10 +1932,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules range le seau. Papa lui tend la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino range le seau.
+narrateur|Il range la pelle.
+narrateur|Papa lui tend la main.
+papa|Tu as fini le gâteau ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|On rentre.
+narrateur|Nino prend la main de papa.
+narrateur|Le seau jaune tape doucement.
+narrateur|L'herbe sent encore la pluie.
+papa|Tu es resté où je vois.
+enfant-m|Dans l'espace montré.
+papa|Oui.
+papa|L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,7 +1972,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau jaune rentre à la maison. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,10 +2112,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le seau jaune rentre à la maison.
+enfant-m|J'ai fait un gâteau.
+papa|Oui.
+papa|Dans l'espace montré.
+papa|Bravo, Nino.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un seau jaune attend près des bottes. Les bottes sont un peu mouillées. Le pain sent bon, loin. L'herbe sent la pluie. Une feuille est collée sur une botte. Tu as vu le seau, Nino ? Il est jaune, papa. Oui. On le prend. Nino prend le seau. Le plastique est lisse. La pelle est dedans. La pelle est rouge. On met tes bottes ? Nino enfile une botte. Puis l'autre botte. Tu as fini tes bottes ? Oui, papa. Bravo. Ils marchent vers le parc. Une goutte tombe d'une feuille. Elle fait tic sur le seau. Tic. Oui. C'est une goutte. En ce moment, ils arrivent au parc. Le bac à sable est là. Le sable est frais. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nino va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Le banc est un peu humide. Papa voit Nino. L'adulte voit. Nino verse le sable. Le sable est frais et un peu froid. Il est froid, papa. Oui. Il est frais. Nino fait un gâteau. Il tape le seau. Ça fait toc toc. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Nino retourne le seau. Le gâteau de sable est là. Il est un peu croulé. Un gâteau ! Beau gâteau. L'adulte voit. Tu as fait du bon travail. Nino reste dans l'espace. Les mains sont dans le sable. Le seau jaune brille un peu. On fait un autre gâteau ? Oui. Nino remplit encore le seau. Il tasse avec la pelle rouge. Il retourne encore le seau. Je te vois encore. Je reste ici. Oui. Dans l'espace montré.</t>
+          <t>Un seau jaune attend près des bottes. Les bottes sont un peu mouillées. Le pain sent bon, loin. L'herbe sent la pluie. Une feuille est collée sur une botte. Tu as vu le seau, Nino ? Il est jaune, papa. Oui. On le prend. Nino prend le seau. Le plastique est lisse. La pelle est dedans. La pelle est rouge. On met tes bottes ? Nino enfile une botte. Puis l'autre botte. Tu as fini tes bottes ? Oui, papa. Bravo. Ils marchent vers le parc. Une goutte tombe d'une feuille. Elle fait tic sur le seau. Tic. Oui. C'est une goutte. En ce moment, ils arrivent au parc. Le bac à sable est là. Le sable est frais. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nino va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Le banc est un peu humide. Papa voit Nino. L'adulte voit. Nino verse le sable. Le sable est frais et un peu froid. Il est froid, papa. Oui. Il est frais. Nino fait un gâteau. Il tape le seau. Ça fait toc toc. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Nino retourne le seau. Le gâteau de sable est là. Il est un peu croulé. Un gâteau ! Beau gâteau. L'adulte voit. Nino reste dans l'espace. Les mains sont dans le sable. Le seau jaune brille un peu. On fait un autre gâteau ? Oui. Nino remplit encore le seau. Il tasse avec la pelle rouge. Il retourne encore le seau. Je te vois encore. Je reste ici. Oui. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules arrive au parc. Papa lui montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. Papa dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Jules va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Papa voit Jules. L'adulte voit. Jules verse le sable. Il fait un gâteau. Le sable est frais. Jules reste dans l'espace. Papa dit : je te vois. Jules sourit. Il reste là. Les mains sont dans le sable.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un seau jaune attend près des bottes. Les bottes sont un peu mouillées. Le pain sent bon, loin. L'herbe sent la pluie. Une feuille est collée sur une botte. Tu as vu le seau, Nino ? Il est jaune, papa. Oui. On le prend. Nino prend le seau. Le plastique est lisse. La pelle est dedans. La pelle est rouge. On met tes bottes ? Nino enfile une botte. Puis l'autre botte. Tu as fini tes bottes ? Oui, papa. Bravo. Ils marchent vers le parc. Une goutte tombe d'une feuille. Elle fait tic sur le seau. Tic. Oui. C'est une goutte. En ce moment, ils arrivent au parc. Le bac à sable est là. Le sable est frais. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nino va au bac à sable. Il reste dans l'espace montré. Papa s'assoit sur le banc. Le banc est un peu humide. Papa voit Nino. L'adulte voit. Nino verse le sable. Le sable est frais et un peu froid. Il est froid, papa. Oui. Il est frais. Nino fait un gâteau. Il tape le seau. Ça fait toc toc. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Nino retourne le seau. Le gâteau de sable est là. Il est un peu croulé. Un gâteau ! Beau gâteau. L'adulte voit. Nino reste dans l'espace. Les mains sont dans le sable. Le seau jaune brille un peu. On fait un autre gâteau ? Oui. Nino remplit encore le seau. Il tasse avec la pelle rouge. Il retourne encore le seau. Je te vois encore. Je reste ici. Oui. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 enfant-m|Un gâteau !
 papa|Beau gâteau.
 papa|L'adulte voit.
-papa|Tu as fait du bon travail.
 narrateur|Nino reste dans l'espace.
 narrateur|Les mains sont dans le sable.
 narrateur|Le seau jaune brille un peu.
@@ -1428,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules joue au parc. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino joue au parc. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1617,7 +1616,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules est dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Papa le voit. Le gâteau de sable est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino est dans l'espace montré. Papa le voit. L'adulte voit. Le gâteau de sable est là. Tu as joué dans l'espace montré ? Oui. Bravo. Je te voyais. Le seau jaune a du sable. La pelle est à côté.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1797,7 +1796,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules range le seau. Papa lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino range le seau. Il range la pelle. Papa lui tend la main. Tu as fini le gâteau ? Oui, papa. Bravo. On rentre. Nino prend la main de papa. Le seau jaune tape doucement. L'herbe sent encore la pluie. Tu es resté où je vois. Dans l'espace montré. Oui. L'adulte voit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1972,12 +1971,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le seau jaune rentre à la maison. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nino. L'histoire est finie.</t>
+          <t>Le seau jaune rentre à la maison. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le seau jaune rentre à la maison. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2116,8 +2115,7 @@
 enfant-m|J'ai fait un gâteau.
 papa|Oui.
 papa|Dans l'espace montré.
-papa|Bravo, Nino.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Nino.</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2181,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
